--- a/Precios.xlsx
+++ b/Precios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://premecol-my.sharepoint.com/personal/ezequielmarollo_premecol_onmicrosoft_com/Documents/Proyectos/Cotizador Terrazo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="11_AD4D2F04E46CFB4ACB3E20C29552CDFC693EDF15" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D16125FA-2808-48EC-A079-B5D46DB0B8F3}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="11_AD4D2F04E46CFB4ACB3E20C29552CDFC693EDF15" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21D3F31D-5608-4B57-95B7-4448187E2260}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Código</t>
   </si>
@@ -177,15 +177,9 @@
     <t>1008002    L5</t>
   </si>
   <si>
-    <t>Consolidante Sellador - 5 lts</t>
-  </si>
-  <si>
     <t>Consolidante Sellador - 20 lts</t>
   </si>
   <si>
-    <t>1008003    L5</t>
-  </si>
-  <si>
     <t>1008003    L2</t>
   </si>
   <si>
@@ -196,6 +190,9 @@
   </si>
   <si>
     <t xml:space="preserve">Tec Puente Adh. Componente B - 15 kg </t>
+  </si>
+  <si>
+    <t>lista oct/26</t>
   </si>
 </sst>
 </file>
@@ -287,8 +284,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4AA24436-D3D7-467E-AB97-5C144176416C}" name="precios" displayName="precios" ref="A1:C29" totalsRowShown="0">
-  <autoFilter ref="A1:C29" xr:uid="{4AA24436-D3D7-467E-AB97-5C144176416C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4AA24436-D3D7-467E-AB97-5C144176416C}" name="precios" displayName="precios" ref="A1:C28" totalsRowShown="0">
+  <autoFilter ref="A1:C28" xr:uid="{4AA24436-D3D7-467E-AB97-5C144176416C}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{57889441-D99A-4A27-891A-A47D845FD523}" name="Código" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{A7D21DBD-F0DD-4F9C-9701-8D619069C9F1}" name="Descripción"/>
@@ -561,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" style="2" customWidth="1"/>
@@ -569,7 +566,7 @@
     <col min="3" max="3" width="11.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -579,8 +576,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -588,10 +588,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="1">
-        <v>44316.11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -599,10 +599,10 @@
         <v>4</v>
       </c>
       <c r="C3" s="1">
-        <v>65531.65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>62652</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -610,10 +610,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="1">
-        <v>65531.65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>62652</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -621,10 +621,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>65531.65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>62652</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -632,10 +632,10 @@
         <v>7</v>
       </c>
       <c r="C6" s="1">
-        <v>72081.52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>62652</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -643,10 +643,10 @@
         <v>21</v>
       </c>
       <c r="C7" s="1">
-        <v>12125.52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10641</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -654,10 +654,10 @@
         <v>22</v>
       </c>
       <c r="C8" s="1">
-        <v>14616.64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>16206</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -665,10 +665,10 @@
         <v>23</v>
       </c>
       <c r="C9" s="1">
-        <v>14616.64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>23293</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -676,10 +676,10 @@
         <v>24</v>
       </c>
       <c r="C10" s="1">
-        <v>14616.64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>16611</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -687,10 +687,10 @@
         <v>25</v>
       </c>
       <c r="C11" s="1">
-        <v>20592.55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21766</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -698,10 +698,10 @@
         <v>26</v>
       </c>
       <c r="C12" s="1">
-        <v>20592.55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19437</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -709,10 +709,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="1">
-        <v>20592.55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>28254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -720,10 +720,10 @@
         <v>28</v>
       </c>
       <c r="C14" s="1">
-        <v>26576.48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26228</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>37</v>
       </c>
@@ -731,10 +731,10 @@
         <v>29</v>
       </c>
       <c r="C15" s="1">
-        <v>12125.52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>38</v>
       </c>
@@ -742,7 +742,7 @@
         <v>30</v>
       </c>
       <c r="C16" s="1">
-        <v>14616.64</v>
+        <v>16206</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,7 +753,7 @@
         <v>31</v>
       </c>
       <c r="C17" s="1">
-        <v>14616.64</v>
+        <v>24411</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,7 +764,7 @@
         <v>32</v>
       </c>
       <c r="C18" s="1">
-        <v>14616.64</v>
+        <v>16831</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,7 +775,7 @@
         <v>33</v>
       </c>
       <c r="C19" s="1">
-        <v>20592.55</v>
+        <v>22260</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,7 +786,7 @@
         <v>36</v>
       </c>
       <c r="C20" s="1">
-        <v>20592.55</v>
+        <v>19804</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,7 +797,7 @@
         <v>34</v>
       </c>
       <c r="C21" s="1">
-        <v>20592.55</v>
+        <v>27388</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,7 +808,7 @@
         <v>35</v>
       </c>
       <c r="C22" s="1">
-        <v>26576.48</v>
+        <v>26786</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -816,10 +816,10 @@
         <v>1101004</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1">
-        <v>18821</v>
+        <v>28308</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -827,10 +827,10 @@
         <v>1101005</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C24" s="1">
-        <v>138550</v>
+        <v>220480</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,7 +841,7 @@
         <v>45</v>
       </c>
       <c r="C25" s="1">
-        <v>25380</v>
+        <v>15478</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,7 +852,7 @@
         <v>48</v>
       </c>
       <c r="C26" s="1">
-        <v>92430</v>
+        <v>61912</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -860,32 +860,21 @@
         <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C27" s="1">
-        <v>124203</v>
+        <v>184764</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
         <v>50</v>
       </c>
       <c r="C28" s="1">
-        <v>16193</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="1">
-        <v>54147</v>
+        <v>394748</v>
       </c>
     </row>
   </sheetData>
